--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/sep-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/sep-2026.xlsx
@@ -623,7 +623,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +883,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +948,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1013,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1078,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1143,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1208,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1273,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1338,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1464,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1529,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1594,11 @@
           <t>77.720.988-4</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1659,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1724,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1789,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1854,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1919,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1984,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2049,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2114,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2240,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2305,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2370,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2435,11 @@
           <t>78.085.401-4</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2500,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2626,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2691,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2756,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2821,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3008,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3073,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3138,11 @@
           <t>78.085.401-4</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3203,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3268,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3333,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3398,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3463,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3528,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3593,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3658,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3723,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3788,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3853,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3918,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3983,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4109,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4174,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4239,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4304,11 @@
           <t>78.085.401-4</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4369,11 @@
           <t>78.085.401-4</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4434,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4499,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4564,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4629,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4755,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4820,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4885,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +5011,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5076,11 @@
           <t>78.085.401-4</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5141,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5206,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5332,11 @@
           <t>77.720.988-4</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5397,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5462,11 @@
           <t>78.085.401-4</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5527,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5592,11 @@
           <t>78.067.906-9</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5657,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5722,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5787,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5852,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5917,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5982,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6047,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6112,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6238,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6303,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6368,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6494,11 @@
           <t>78.085.401-4</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6620,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6685,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6750,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6815,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6941,11 @@
           <t>78.085.401-4</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +7006,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7071,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7136,11 @@
           <t>78.085.401-4</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7201,11 @@
           <t>78.085.401-4</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7266,11 @@
           <t>78.085.401-4</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7331,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7396,11 @@
           <t>78.085.401-4</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7461,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7526,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7591,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7656,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7721,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7786,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7851,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7916,11 @@
           <t>78.085.401-4</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +8042,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8107,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8172,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8237,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8302,11 @@
           <t>78.085.401-4</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8367,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8432,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8558,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8623,11 @@
           <t>77.529.681-K</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8688,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8875,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8940,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +9005,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +9070,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9196,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9261,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9387,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9452,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9700,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9765,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9830,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9895,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9960,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +10025,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10212,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10277,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10342,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10407,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10472,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10598,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10724,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10850,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +10915,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +10980,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +11045,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +11110,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +11175,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11301,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11366,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11431,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11557,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11622,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11687,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11752,11 @@
           <t>78.085.401-4</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11817,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11882,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +11947,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +12012,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +12077,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +12142,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +12207,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12272,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12337,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12402,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12467,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12532,11 @@
           <t>78.085.401-4</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12597,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12723,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12788,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12853,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +12918,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +12983,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +13048,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +13113,11 @@
           <t>78.085.401-4</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +13178,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13365,11 @@
           <t>77.988.165-2</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13491,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13556,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13621,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13686,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13751,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +13877,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +13942,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +14007,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +14072,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +14137,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +14202,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +14267,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +14332,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14397,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14462,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14527,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14653,11 @@
           <t>78.085.401-4</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14718,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14783,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14848,11 @@
           <t>77.809.872-5</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +14974,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +15039,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +15104,11 @@
           <t>76.317.833-1</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +15169,11 @@
           <t>77.042.972-2</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +15234,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +15299,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15364,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15429,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15494,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15559,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15624,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15750,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15815,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15080,7 +15880,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15141,7 +15945,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +16071,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +16136,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +16201,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +16266,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +16331,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +16396,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +16461,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16526,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16591,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15812,7 +16656,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16721,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16786,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15995,7 +16851,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16056,7 +16916,11 @@
           <t>78.085.401-4</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +16981,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +17046,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +17111,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +17176,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +17241,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +17306,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +17371,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17436,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +17501,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17566,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17631,11 @@
           <t>78.085.401-4</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17696,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17822,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +17887,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +17952,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +18078,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17215,7 +18143,11 @@
           <t>78.085.401-4</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17276,7 +18208,11 @@
           <t>77.547.396-7</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17337,7 +18273,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17398,7 +18338,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17459,7 +18403,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17520,7 +18468,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17581,7 +18533,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18659,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17764,7 +18724,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17825,7 +18789,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17886,7 +18854,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17947,7 +18919,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +18984,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18069,7 +19049,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18130,7 +19114,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18191,7 +19179,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18252,7 +19244,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18313,7 +19309,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +19374,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18435,7 +19439,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18496,7 +19504,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18557,7 +19569,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +19634,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18740,7 +19760,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18801,7 +19825,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18862,7 +19890,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18923,7 +19955,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18984,7 +20020,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19045,7 +20085,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19106,7 +20150,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19228,7 +20276,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +20341,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19350,7 +20406,11 @@
           <t>78.085.401-4</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19411,7 +20471,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19472,7 +20536,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19533,7 +20601,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19594,7 +20666,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19655,7 +20731,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19716,7 +20796,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +20922,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19960,7 +21048,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20021,7 +21113,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20143,7 +21239,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20204,7 +21304,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20265,7 +21369,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20326,7 +21434,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20387,7 +21499,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20448,7 +21564,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20509,7 +21629,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20570,7 +21694,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20631,7 +21759,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20692,7 +21824,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20753,7 +21889,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20814,7 +21954,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20936,7 +22080,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20997,7 +22145,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21119,7 +22271,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21180,7 +22336,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21241,7 +22401,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21302,7 +22466,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21363,7 +22531,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21424,7 +22596,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21485,7 +22661,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21546,7 +22726,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21672,7 +22856,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21794,7 +22982,11 @@
           <t>78.069.505-6</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21855,7 +23047,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21916,7 +23112,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21977,7 +23177,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22038,7 +23242,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22099,7 +23307,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22160,7 +23372,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22221,7 +23437,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22282,7 +23502,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22343,7 +23567,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22465,7 +23693,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22526,7 +23758,11 @@
           <t>78.085.401-4</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22587,7 +23823,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22648,7 +23888,11 @@
           <t>78.085.401-4</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22709,7 +23953,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22770,7 +24018,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22831,7 +24083,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22892,7 +24148,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22953,7 +24213,11 @@
           <t>77.988.165-2</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23014,7 +24278,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23136,7 +24404,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23258,7 +24530,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23319,7 +24595,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23441,7 +24721,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23502,7 +24786,11 @@
           <t>77.809.872-5</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23563,7 +24851,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23624,7 +24916,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23685,7 +24981,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23746,7 +25046,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23807,7 +25111,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23868,7 +25176,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23929,7 +25241,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23990,7 +25306,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24112,7 +25432,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24173,7 +25497,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24234,7 +25562,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24295,7 +25627,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24356,7 +25692,11 @@
           <t>78.094.613-K</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24417,7 +25757,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24478,7 +25822,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24539,7 +25887,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24783,7 +26135,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24844,7 +26200,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24905,7 +26265,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25088,7 +26452,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25210,7 +26578,11 @@
           <t>78.085.401-4</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25271,7 +26643,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25332,7 +26708,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25454,7 +26834,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25515,7 +26899,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25576,7 +26964,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25637,7 +27029,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25698,7 +27094,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25759,7 +27159,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25820,7 +27224,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25942,7 +27350,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26003,7 +27415,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26064,7 +27480,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26125,7 +27545,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26186,7 +27610,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26247,7 +27675,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26308,7 +27740,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26369,7 +27805,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26491,7 +27931,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26552,7 +27996,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26613,7 +28061,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26674,7 +28126,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26735,7 +28191,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26796,7 +28256,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26857,7 +28321,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26979,7 +28447,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27040,7 +28512,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27101,7 +28577,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27162,7 +28642,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27223,7 +28707,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27284,7 +28772,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27345,7 +28837,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27467,7 +28963,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27528,7 +29028,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27589,7 +29093,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27650,7 +29158,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27711,7 +29223,11 @@
           <t>78.085.401-4</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27772,7 +29288,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27833,7 +29353,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27894,7 +29418,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27955,7 +29483,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28016,7 +29548,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28138,7 +29674,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28199,7 +29739,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28321,7 +29865,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28382,7 +29930,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28443,7 +29995,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28504,7 +30060,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28565,7 +30125,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28626,7 +30190,11 @@
           <t>78.094.613-K</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28687,7 +30255,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28748,7 +30320,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28809,7 +30385,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28870,7 +30450,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28931,7 +30515,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29053,7 +30641,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29114,7 +30706,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29175,7 +30771,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29236,7 +30836,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29297,7 +30901,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29358,7 +30966,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29541,7 +31153,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29602,7 +31218,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29663,7 +31283,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29724,7 +31348,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29785,7 +31413,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L481" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29846,7 +31478,11 @@
           <t>78.085.401-4</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29907,7 +31543,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29968,7 +31608,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30029,7 +31673,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30090,7 +31738,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30151,7 +31803,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30212,7 +31868,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30273,7 +31933,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30334,7 +31998,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30395,7 +32063,11 @@
           <t>77.988.165-2</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30456,7 +32128,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30517,7 +32193,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30578,7 +32258,11 @@
           <t>77.649.678-2</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30639,7 +32323,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30700,7 +32388,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30761,7 +32453,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30822,7 +32518,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30883,7 +32583,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31066,7 +32770,11 @@
           <t>77.649.678-2</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31127,7 +32835,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31188,7 +32900,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31249,7 +32965,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31310,7 +33030,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31371,7 +33095,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31432,7 +33160,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31493,7 +33225,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31554,7 +33290,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31615,7 +33355,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31737,7 +33481,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31798,7 +33546,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31859,7 +33611,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L515" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31920,7 +33676,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31981,7 +33741,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32042,7 +33806,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L518" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32103,7 +33871,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32164,7 +33936,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32225,7 +34001,11 @@
           <t>77.979.117-3</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32286,7 +34066,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32347,7 +34131,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32408,7 +34196,11 @@
           <t>78.094.613-K</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L524" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32469,7 +34261,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
